--- a/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_36-2024_01.xlsx
+++ b/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_36-2024_01.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="201">
   <si>
     <t>PAGO</t>
   </si>
@@ -76,7 +76,7 @@
     <t>SCOTIABANK</t>
   </si>
   <si>
-    <t xml:space="preserve">JORGE MANRIQUEZ CUEVAS  </t>
+    <t>JORGE  MANRIQUEZ  CUEVAS</t>
   </si>
   <si>
     <t>012580028661136560</t>
@@ -91,6 +91,15 @@
     <t>BANAMEX</t>
   </si>
   <si>
+    <t>RODOLFO  GALVEZ  BARRIOS</t>
+  </si>
+  <si>
+    <t>127540013217746396</t>
+  </si>
+  <si>
+    <t>AZTECA</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARIA LORETO TORRES QUIRÓZ  </t>
   </si>
   <si>
@@ -106,10 +115,10 @@
     <t>002180701819195488</t>
   </si>
   <si>
-    <t>LUCINA MARIA AURORA  RODRIGUEZ  MERIDA</t>
-  </si>
-  <si>
-    <t>012580028886932853</t>
+    <t>OLGA LORENA  GOMEZ  FOSADO</t>
+  </si>
+  <si>
+    <t>137290104379143332</t>
   </si>
   <si>
     <t>GERARDO DANIEL   HERMIDA AMADOR</t>
@@ -118,9 +127,6 @@
     <t>127290013759479947</t>
   </si>
   <si>
-    <t>AZTECA</t>
-  </si>
-  <si>
     <t>MA. ELIA  MENDEZ  PADRON</t>
   </si>
   <si>
@@ -130,6 +136,18 @@
     <t>SANTANDER</t>
   </si>
   <si>
+    <t xml:space="preserve">LEODEGARIA MENDEZ PADRON  </t>
+  </si>
+  <si>
+    <t>127700013552927500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARIO REYES LOPEZ  </t>
+  </si>
+  <si>
+    <t>002180701906484413</t>
+  </si>
+  <si>
     <t>ESPERANZA GUADALUPE  BERNABE  PAZ</t>
   </si>
   <si>
@@ -142,6 +160,12 @@
     <t>127528013932219641</t>
   </si>
   <si>
+    <t>MARIA DEL CARMEN TORRES OROZCO</t>
+  </si>
+  <si>
+    <t>012528011651278151</t>
+  </si>
+  <si>
     <t>ROCIO  SALINAS  TAPIA</t>
   </si>
   <si>
@@ -154,58 +178,40 @@
     <t>127180016468947576</t>
   </si>
   <si>
+    <t>EMILIANO CHAVEZ TORRES</t>
+  </si>
+  <si>
+    <t>137028170009517816</t>
+  </si>
+  <si>
     <t>DAVID MEDINA DIRCIO</t>
   </si>
   <si>
     <t>137544103175015667</t>
   </si>
   <si>
-    <t>IGNACIO   ESLAVA SANCHEZ</t>
-  </si>
-  <si>
-    <t>127550013018836592</t>
-  </si>
-  <si>
     <t>JOSE DE JESUS  VARELA  SANCHEZ</t>
   </si>
   <si>
     <t>127180016777382411</t>
   </si>
   <si>
-    <t>PAOLA ESMERALDA  PADILLA  VAZQUEZ</t>
-  </si>
-  <si>
-    <t>012528015519308774</t>
-  </si>
-  <si>
-    <t>LIOVA  RODRIGUEZ  RIOS</t>
-  </si>
-  <si>
-    <t>137290103156690876</t>
-  </si>
-  <si>
     <t xml:space="preserve">ROSA MARÍA CORTÉS PÉREZ  </t>
   </si>
   <si>
     <t>012095004630291071</t>
   </si>
   <si>
-    <t xml:space="preserve">ADRIANA GUADALUPE CISNEROS ESTRADA  </t>
+    <t>ADRIANA GUADALUPE  CISNEROS  ESTRADA</t>
   </si>
   <si>
     <t>012542027401132048</t>
   </si>
   <si>
-    <t xml:space="preserve">SONIA VILLASEÑOR CHAIREZ  </t>
-  </si>
-  <si>
-    <t>137095100128029149</t>
-  </si>
-  <si>
-    <t>OFELIA  TAMAYO  MEDRANO</t>
-  </si>
-  <si>
-    <t>127261013065980609</t>
+    <t>ROSARIO   YEME LÓPEZ</t>
+  </si>
+  <si>
+    <t>137090103227994766</t>
   </si>
   <si>
     <t xml:space="preserve">ERIKA TEMES GONZALEZ  </t>
@@ -232,7 +238,7 @@
     <t>127320013008867426</t>
   </si>
   <si>
-    <t xml:space="preserve">MAGALLY RODRIGUEZ SILVA  </t>
+    <t>MAGALLY  RODRIGUEZ  SILVA</t>
   </si>
   <si>
     <t>127320013939074456</t>
@@ -250,27 +256,18 @@
     <t>012320029389721173</t>
   </si>
   <si>
-    <t xml:space="preserve">NORMA FILOMENA VILLASEÑOR ROMAN  </t>
+    <t>NORMA FILOMENA  VILLASEÑOR  ROMAN</t>
   </si>
   <si>
     <t>127320013081186470</t>
   </si>
   <si>
-    <t xml:space="preserve">ABRIL BASILIO NAVARRETE  </t>
+    <t>ABRIL  BASILIO  NAVARRETE</t>
   </si>
   <si>
     <t>127542013228517473</t>
   </si>
   <si>
-    <t>MA REINA  ALCOCER  NAVA</t>
-  </si>
-  <si>
-    <t>062260008177776940</t>
-  </si>
-  <si>
-    <t>AFIRME</t>
-  </si>
-  <si>
     <t>HUMBERTA  TORRES  MANCILLA</t>
   </si>
   <si>
@@ -283,19 +280,7 @@
     <t>012180015117736254</t>
   </si>
   <si>
-    <t xml:space="preserve">KARLA GABRIELA MENESES SANCHEZ  </t>
-  </si>
-  <si>
-    <t>012180015076724695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIO ROBLES QUINTANA  </t>
-  </si>
-  <si>
-    <t>012760026196083706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATRICIA ALCOCER CARVAJAL  </t>
+    <t>PATRICIA  ALCOCER  CARVAJAL</t>
   </si>
   <si>
     <t>012261015561538956</t>
@@ -319,6 +304,12 @@
     <t>127320013555441052</t>
   </si>
   <si>
+    <t>NATALIO   CABRERA SANCHEZ</t>
+  </si>
+  <si>
+    <t>012497027389657143</t>
+  </si>
+  <si>
     <t>CYNTHIA VERÓNICA  MORENO  HERNÁNDEZ</t>
   </si>
   <si>
@@ -331,12 +322,24 @@
     <t>012497015360493037</t>
   </si>
   <si>
-    <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
+    <t>RAQUEL  LUGO  ARGUETA</t>
+  </si>
+  <si>
+    <t>137220103191272892</t>
+  </si>
+  <si>
+    <t>MANUEL DE JESUS  CASTALDI  PEREZ</t>
   </si>
   <si>
     <t>127131013606487141</t>
   </si>
   <si>
+    <t>SALOME ESPERANZA  RODRIGUEZ  SALINAS</t>
+  </si>
+  <si>
+    <t>137261100363660744</t>
+  </si>
+  <si>
     <t xml:space="preserve">OSCAR RENATO VARELA PÉREZ  </t>
   </si>
   <si>
@@ -349,10 +352,22 @@
     <t>127798013739309568</t>
   </si>
   <si>
-    <t xml:space="preserve">ALICIA LEON MORALES  </t>
-  </si>
-  <si>
-    <t>137798100125613800</t>
+    <t>ROBERTO CARLOS  RAMIREZ  MORALES</t>
+  </si>
+  <si>
+    <t>137650103970141219</t>
+  </si>
+  <si>
+    <t>SANDRA LUZ SANCHEZ MEDINA</t>
+  </si>
+  <si>
+    <t>127902013719562645</t>
+  </si>
+  <si>
+    <t>SUSANA  SANDOVAL  LUGO</t>
+  </si>
+  <si>
+    <t>137497104749100708</t>
   </si>
   <si>
     <t>SONIA    MENDOZA SANCHEZ</t>
@@ -361,42 +376,36 @@
     <t>127022013794381514</t>
   </si>
   <si>
-    <t>MARIA ELIZABETH  MANDUJANO  HERNANDEZ</t>
-  </si>
-  <si>
-    <t>127180013262478503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE BORRAYO RAMIREZ  </t>
-  </si>
-  <si>
-    <t>012320015027552113</t>
-  </si>
-  <si>
     <t>EZEQUIEL   CAMAS  SALAYA</t>
   </si>
   <si>
     <t>137798100490064414</t>
   </si>
   <si>
+    <t xml:space="preserve">JUAN ALEJANDRO  ABARCA SANCHEZ  </t>
+  </si>
+  <si>
+    <t>127490013379163828</t>
+  </si>
+  <si>
     <t>PATRICIA PABLO  VÁZQUEZ</t>
   </si>
   <si>
     <t>012180014334874233</t>
   </si>
   <si>
+    <t>ALEJANDRINA   MENDOZA   MARTINEZ</t>
+  </si>
+  <si>
+    <t>137040100725667056</t>
+  </si>
+  <si>
     <t>MIGUEL ALBERTO  PALMA  CHUM</t>
   </si>
   <si>
     <t>137798103294273961</t>
   </si>
   <si>
-    <t>MARIA DEL CARMEN     MORALES MONTOYA</t>
-  </si>
-  <si>
-    <t>127180016076680393</t>
-  </si>
-  <si>
     <t>AURELIA GARCIA GARCIA</t>
   </si>
   <si>
@@ -409,37 +418,91 @@
     <t>137542104464955727</t>
   </si>
   <si>
+    <t>PAMELA  CASTALDI  GONZALEZ</t>
+  </si>
+  <si>
+    <t>127100013413288797</t>
+  </si>
+  <si>
+    <t>MARIA EVANGELINA  NAVARRO  OSORIO</t>
+  </si>
+  <si>
+    <t>012320029440641354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROCIO ZORAIDA JAIMEZ RODR?GUEZ  </t>
+  </si>
+  <si>
+    <t>012320015810346727</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARGARITO VENCES  ALBINO  </t>
   </si>
   <si>
     <t>137497103545128532</t>
   </si>
   <si>
+    <t>CRUZ  VIVEROS  SANCHEZ</t>
+  </si>
+  <si>
+    <t>127497013437893758</t>
+  </si>
+  <si>
     <t>GLORIA RODRÍGUEZ  BAUTISTA</t>
   </si>
   <si>
     <t>137497104927006954</t>
   </si>
   <si>
-    <t>MA.GUADALUPE  FLORES  MENDOZA</t>
-  </si>
-  <si>
-    <t>137497100640487469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABRIELA HERNÁNDEZ CASTILLO  </t>
+    <t>GUILLERMINA GABRIELA   ARAGON  SANCHEZ</t>
+  </si>
+  <si>
+    <t>127542013753215208</t>
+  </si>
+  <si>
+    <t>GABRIELA   HERNÁNDEZ CASTILLO</t>
   </si>
   <si>
     <t>127542013490844330</t>
   </si>
   <si>
-    <t xml:space="preserve">JUAN JOSE RUEDA DE LEON ROMERO  </t>
-  </si>
-  <si>
-    <t>137798100115795961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MITZUQUI YAJAYRA GALVÁN ZARATE  </t>
+    <t>CRESCENCIA  LEON HERNANDEZ</t>
+  </si>
+  <si>
+    <t>137798100107628428</t>
+  </si>
+  <si>
+    <t>MICAELA  ARIAS LOPEZ</t>
+  </si>
+  <si>
+    <t>137798100237963558</t>
+  </si>
+  <si>
+    <t>IRMA  OSNAYA VALDEZ</t>
+  </si>
+  <si>
+    <t>127497013068374882</t>
+  </si>
+  <si>
+    <t>ROGELIO RAUL  MARTINEZ  PROVISOR</t>
+  </si>
+  <si>
+    <t>127547013535145708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANCY RUIZ AGUILAR  </t>
+  </si>
+  <si>
+    <t>137542103083265307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA MARIA DEL REFUGIO RODRIGUEZ BALANDRAN  </t>
+  </si>
+  <si>
+    <t>012180015397570366</t>
+  </si>
+  <si>
+    <t>MITZUQUI YAJAYRA  GALVÁN  ZARATE</t>
   </si>
   <si>
     <t>137320104157672649</t>
@@ -460,7 +523,7 @@
     <t>CONCEPTO DE FACTURA</t>
   </si>
   <si>
-    <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
+    <t>LUIS ALBERTO  LIN  SALINAS</t>
   </si>
   <si>
     <t>012180015558104539</t>
@@ -475,7 +538,7 @@
     <t>012528015192771346</t>
   </si>
   <si>
-    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
+    <t>SOFIA  BARROSO  RUIZ</t>
   </si>
   <si>
     <t>012261004726315475</t>
@@ -517,7 +580,7 @@
     <t>PROMOCIÓN, DISPOSICIÓN Y PUBLICIDAD VENTAS BENELEIT</t>
   </si>
   <si>
-    <t xml:space="preserve">RENE JAVIER MEDRANO LOPEZ  </t>
+    <t>RENE JAVIER   MEDRANO LOPEZ</t>
   </si>
   <si>
     <t>012650028495052889</t>
@@ -535,7 +598,7 @@
     <t>002528701665393643</t>
   </si>
   <si>
-    <t xml:space="preserve">BENJAMIN RAUL PADILLA BARRAGÁN  </t>
+    <t>BENJAMIN RAUL  PADILLA  BARRAGÁN</t>
   </si>
   <si>
     <t>002528700329964759</t>
@@ -941,12 +1004,12 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
     <col min="2" max="2" width="10.426" bestFit="true" customWidth="true" style="1"/>
-    <col min="3" max="3" width="45.846" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="56.558" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="2"/>
     <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="1"/>
     <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="1"/>
@@ -994,7 +1057,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>26790</v>
+        <v>68128</v>
       </c>
       <c r="B2" s="1">
         <v>1373</v>
@@ -1029,7 +1092,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>26777</v>
+        <v>68116</v>
       </c>
       <c r="B3" s="1">
         <v>3146</v>
@@ -1050,13 +1113,13 @@
         <v>18</v>
       </c>
       <c r="H3" s="3">
-        <v>583.0</v>
+        <v>558.0</v>
       </c>
       <c r="I3" s="3">
-        <v>29.61</v>
+        <v>28.01</v>
       </c>
       <c r="J3" s="3">
-        <v>553.39</v>
+        <v>529.99</v>
       </c>
       <c r="K3" t="s">
         <v>15</v>
@@ -1064,7 +1127,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>26791</v>
+        <v>68129</v>
       </c>
       <c r="B4" s="1">
         <v>4209</v>
@@ -1099,7 +1162,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>26809</v>
+        <v>68144</v>
       </c>
       <c r="B5" s="1">
         <v>5841</v>
@@ -1134,10 +1197,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>26753</v>
+        <v>68088</v>
       </c>
       <c r="B6" s="1">
-        <v>8272</v>
+        <v>7815</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -1155,13 +1218,13 @@
         <v>26</v>
       </c>
       <c r="H6" s="3">
-        <v>1825.8</v>
+        <v>275.0</v>
       </c>
       <c r="I6" s="3">
-        <v>125.62</v>
+        <v>9.9</v>
       </c>
       <c r="J6" s="3">
-        <v>1700.18</v>
+        <v>265.1</v>
       </c>
       <c r="K6" t="s">
         <v>15</v>
@@ -1169,10 +1232,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>26776</v>
+        <v>68094</v>
       </c>
       <c r="B7" s="1">
-        <v>12634</v>
+        <v>8272</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -1187,16 +1250,16 @@
         <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3">
-        <v>473.0</v>
+        <v>1825.8</v>
       </c>
       <c r="I7" s="3">
-        <v>22.57</v>
+        <v>125.62</v>
       </c>
       <c r="J7" s="3">
-        <v>450.43</v>
+        <v>1700.18</v>
       </c>
       <c r="K7" t="s">
         <v>15</v>
@@ -1204,16 +1267,16 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>26865</v>
+        <v>68115</v>
       </c>
       <c r="B8" s="1">
-        <v>15432</v>
+        <v>12634</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1">
         <v>30</v>
@@ -1222,16 +1285,16 @@
         <v>13</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H8" s="3">
-        <v>150.0</v>
+        <v>473.0</v>
       </c>
       <c r="I8" s="3">
-        <v>2.88</v>
+        <v>22.57</v>
       </c>
       <c r="J8" s="3">
-        <v>147.12</v>
+        <v>450.43</v>
       </c>
       <c r="K8" t="s">
         <v>15</v>
@@ -1239,16 +1302,16 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>26820</v>
+        <v>68152</v>
       </c>
       <c r="B9" s="1">
-        <v>17042</v>
+        <v>14975</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="1">
         <v>30</v>
@@ -1257,16 +1320,16 @@
         <v>13</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H9" s="3">
-        <v>211.05</v>
+        <v>424.0</v>
       </c>
       <c r="I9" s="3">
-        <v>5.8</v>
+        <v>19.43</v>
       </c>
       <c r="J9" s="3">
-        <v>205.25</v>
+        <v>404.57</v>
       </c>
       <c r="K9" t="s">
         <v>15</v>
@@ -1274,10 +1337,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>26789</v>
+        <v>68151</v>
       </c>
       <c r="B10" s="1">
-        <v>18735</v>
+        <v>17042</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
@@ -1292,16 +1355,16 @@
         <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H10" s="3">
-        <v>416.5</v>
+        <v>211.05</v>
       </c>
       <c r="I10" s="3">
-        <v>18.95</v>
+        <v>5.8</v>
       </c>
       <c r="J10" s="3">
-        <v>397.55</v>
+        <v>205.25</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
@@ -1309,34 +1372,34 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>26808</v>
+        <v>68127</v>
       </c>
       <c r="B11" s="1">
-        <v>20738</v>
+        <v>18735</v>
       </c>
       <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="1">
+        <v>30</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="1">
-        <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H11" s="3">
-        <v>512.0</v>
+        <v>416.5</v>
       </c>
       <c r="I11" s="3">
-        <v>25.06</v>
+        <v>18.95</v>
       </c>
       <c r="J11" s="3">
-        <v>486.94</v>
+        <v>397.55</v>
       </c>
       <c r="K11" t="s">
         <v>15</v>
@@ -1344,10 +1407,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>26778</v>
+        <v>68162</v>
       </c>
       <c r="B12" s="1">
-        <v>25919</v>
+        <v>18791</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
@@ -1362,16 +1425,16 @@
         <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H12" s="3">
-        <v>595.5</v>
+        <v>178.0</v>
       </c>
       <c r="I12" s="3">
-        <v>30.41</v>
+        <v>3.69</v>
       </c>
       <c r="J12" s="3">
-        <v>565.09</v>
+        <v>174.31</v>
       </c>
       <c r="K12" t="s">
         <v>15</v>
@@ -1379,10 +1442,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>26830</v>
+        <v>68103</v>
       </c>
       <c r="B13" s="1">
-        <v>26189</v>
+        <v>20416</v>
       </c>
       <c r="C13" t="s">
         <v>41</v>
@@ -1397,16 +1460,16 @@
         <v>13</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H13" s="3">
-        <v>51.75</v>
+        <v>308.0</v>
       </c>
       <c r="I13" s="3">
-        <v>0.99</v>
+        <v>12.01</v>
       </c>
       <c r="J13" s="3">
-        <v>50.76</v>
+        <v>295.99</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
@@ -1414,10 +1477,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>26795</v>
+        <v>68143</v>
       </c>
       <c r="B14" s="1">
-        <v>26226</v>
+        <v>20738</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -1432,16 +1495,16 @@
         <v>13</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H14" s="3">
-        <v>1146.0</v>
+        <v>512.0</v>
       </c>
       <c r="I14" s="3">
-        <v>65.64</v>
+        <v>25.06</v>
       </c>
       <c r="J14" s="3">
-        <v>1080.36</v>
+        <v>486.94</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
@@ -1449,10 +1512,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>26794</v>
+        <v>68089</v>
       </c>
       <c r="B15" s="1">
-        <v>26880</v>
+        <v>25919</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -1470,13 +1533,13 @@
         <v>26</v>
       </c>
       <c r="H15" s="3">
-        <v>258.0</v>
+        <v>998.0</v>
       </c>
       <c r="I15" s="3">
-        <v>8.81</v>
+        <v>56.17</v>
       </c>
       <c r="J15" s="3">
-        <v>249.19</v>
+        <v>941.83</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
@@ -1484,10 +1547,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>26793</v>
+        <v>68166</v>
       </c>
       <c r="B16" s="1">
-        <v>27002</v>
+        <v>26120</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
@@ -1502,16 +1565,16 @@
         <v>13</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H16" s="3">
-        <v>86.0</v>
+        <v>224.0</v>
       </c>
       <c r="I16" s="3">
-        <v>1.65</v>
+        <v>6.63</v>
       </c>
       <c r="J16" s="3">
-        <v>84.35</v>
+        <v>217.37</v>
       </c>
       <c r="K16" t="s">
         <v>15</v>
@@ -1519,10 +1582,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>26773</v>
+        <v>68083</v>
       </c>
       <c r="B17" s="1">
-        <v>27736</v>
+        <v>26189</v>
       </c>
       <c r="C17" t="s">
         <v>49</v>
@@ -1537,16 +1600,16 @@
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H17" s="3">
-        <v>1075.5</v>
+        <v>318.85</v>
       </c>
       <c r="I17" s="3">
-        <v>61.13</v>
+        <v>12.7</v>
       </c>
       <c r="J17" s="3">
-        <v>1014.37</v>
+        <v>306.15</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
@@ -1554,10 +1617,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>26807</v>
+        <v>68137</v>
       </c>
       <c r="B18" s="1">
-        <v>28629</v>
+        <v>26226</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
@@ -1572,16 +1635,16 @@
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H18" s="3">
-        <v>25.0</v>
+        <v>1146.0</v>
       </c>
       <c r="I18" s="3">
-        <v>0.48</v>
+        <v>65.64</v>
       </c>
       <c r="J18" s="3">
-        <v>24.52</v>
+        <v>1080.36</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
@@ -1589,10 +1652,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>26826</v>
+        <v>68169</v>
       </c>
       <c r="B19" s="1">
-        <v>29603</v>
+        <v>26397</v>
       </c>
       <c r="C19" t="s">
         <v>53</v>
@@ -1607,16 +1670,16 @@
         <v>13</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H19" s="3">
-        <v>45.35</v>
+        <v>314.0</v>
       </c>
       <c r="I19" s="3">
-        <v>0.87</v>
+        <v>12.39</v>
       </c>
       <c r="J19" s="3">
-        <v>44.48</v>
+        <v>301.61</v>
       </c>
       <c r="K19" t="s">
         <v>15</v>
@@ -1624,10 +1687,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>26825</v>
+        <v>68136</v>
       </c>
       <c r="B20" s="1">
-        <v>30275</v>
+        <v>26880</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -1642,16 +1705,16 @@
         <v>13</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H20" s="3">
-        <v>243.0</v>
+        <v>258.0</v>
       </c>
       <c r="I20" s="3">
-        <v>7.85</v>
+        <v>8.81</v>
       </c>
       <c r="J20" s="3">
-        <v>235.15</v>
+        <v>249.19</v>
       </c>
       <c r="K20" t="s">
         <v>15</v>
@@ -1659,10 +1722,10 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>26806</v>
+        <v>68114</v>
       </c>
       <c r="B21" s="1">
-        <v>30443</v>
+        <v>27736</v>
       </c>
       <c r="C21" t="s">
         <v>57</v>
@@ -1677,16 +1740,16 @@
         <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H21" s="3">
-        <v>1234.6</v>
+        <v>1075.5</v>
       </c>
       <c r="I21" s="3">
-        <v>71.31</v>
+        <v>61.13</v>
       </c>
       <c r="J21" s="3">
-        <v>1163.29</v>
+        <v>1014.37</v>
       </c>
       <c r="K21" t="s">
         <v>15</v>
@@ -1694,10 +1757,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>26823</v>
+        <v>68158</v>
       </c>
       <c r="B22" s="1">
-        <v>30656</v>
+        <v>30275</v>
       </c>
       <c r="C22" t="s">
         <v>59</v>
@@ -1712,16 +1775,16 @@
         <v>13</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H22" s="3">
-        <v>53.0</v>
+        <v>243.0</v>
       </c>
       <c r="I22" s="3">
-        <v>1.02</v>
+        <v>7.85</v>
       </c>
       <c r="J22" s="3">
-        <v>51.98</v>
+        <v>235.15</v>
       </c>
       <c r="K22" t="s">
         <v>15</v>
@@ -1729,10 +1792,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>26857</v>
+        <v>68139</v>
       </c>
       <c r="B23" s="1">
-        <v>31574</v>
+        <v>30443</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
@@ -1747,16 +1810,16 @@
         <v>13</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H23" s="3">
-        <v>81.4</v>
+        <v>1057.6</v>
       </c>
       <c r="I23" s="3">
-        <v>1.56</v>
+        <v>59.98</v>
       </c>
       <c r="J23" s="3">
-        <v>79.84</v>
+        <v>997.62</v>
       </c>
       <c r="K23" t="s">
         <v>15</v>
@@ -1764,10 +1827,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>26843</v>
+        <v>68084</v>
       </c>
       <c r="B24" s="1">
-        <v>31645</v>
+        <v>31150</v>
       </c>
       <c r="C24" t="s">
         <v>63</v>
@@ -1782,16 +1845,16 @@
         <v>13</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H24" s="3">
-        <v>651.2</v>
+        <v>331.0</v>
       </c>
       <c r="I24" s="3">
-        <v>33.97</v>
+        <v>13.48</v>
       </c>
       <c r="J24" s="3">
-        <v>617.23</v>
+        <v>317.52</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
@@ -1799,10 +1862,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>26856</v>
+        <v>68131</v>
       </c>
       <c r="B25" s="1">
-        <v>31689</v>
+        <v>31645</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
@@ -1817,7 +1880,7 @@
         <v>13</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H25" s="3">
         <v>244.2</v>
@@ -1834,10 +1897,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>26770</v>
+        <v>68142</v>
       </c>
       <c r="B26" s="1">
-        <v>31758</v>
+        <v>31689</v>
       </c>
       <c r="C26" t="s">
         <v>67</v>
@@ -1852,16 +1915,16 @@
         <v>13</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H26" s="3">
-        <v>1698.25</v>
+        <v>244.2</v>
       </c>
       <c r="I26" s="3">
-        <v>111.74</v>
+        <v>7.92</v>
       </c>
       <c r="J26" s="3">
-        <v>1586.51</v>
+        <v>236.28</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
@@ -1869,10 +1932,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>26849</v>
+        <v>68111</v>
       </c>
       <c r="B27" s="1">
-        <v>31830</v>
+        <v>31758</v>
       </c>
       <c r="C27" t="s">
         <v>69</v>
@@ -1887,16 +1950,16 @@
         <v>13</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H27" s="3">
-        <v>477.75</v>
+        <v>1698.25</v>
       </c>
       <c r="I27" s="3">
-        <v>22.87</v>
+        <v>111.74</v>
       </c>
       <c r="J27" s="3">
-        <v>454.88</v>
+        <v>1586.51</v>
       </c>
       <c r="K27" t="s">
         <v>15</v>
@@ -1904,10 +1967,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>26860</v>
+        <v>68135</v>
       </c>
       <c r="B28" s="1">
-        <v>31888</v>
+        <v>31830</v>
       </c>
       <c r="C28" t="s">
         <v>71</v>
@@ -1922,16 +1985,16 @@
         <v>13</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H28" s="3">
-        <v>225.0</v>
+        <v>477.75</v>
       </c>
       <c r="I28" s="3">
-        <v>6.7</v>
+        <v>22.87</v>
       </c>
       <c r="J28" s="3">
-        <v>218.3</v>
+        <v>454.88</v>
       </c>
       <c r="K28" t="s">
         <v>15</v>
@@ -1939,10 +2002,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>26772</v>
+        <v>68154</v>
       </c>
       <c r="B29" s="1">
-        <v>33568</v>
+        <v>31888</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
@@ -1957,16 +2020,16 @@
         <v>13</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H29" s="3">
-        <v>249.0</v>
+        <v>225.0</v>
       </c>
       <c r="I29" s="3">
-        <v>8.23</v>
+        <v>6.7</v>
       </c>
       <c r="J29" s="3">
-        <v>240.77</v>
+        <v>218.3</v>
       </c>
       <c r="K29" t="s">
         <v>15</v>
@@ -1974,10 +2037,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>26769</v>
+        <v>68113</v>
       </c>
       <c r="B30" s="1">
-        <v>33949</v>
+        <v>33568</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
@@ -1992,16 +2055,16 @@
         <v>13</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H30" s="3">
-        <v>680.25</v>
+        <v>249.0</v>
       </c>
       <c r="I30" s="3">
-        <v>35.83</v>
+        <v>8.23</v>
       </c>
       <c r="J30" s="3">
-        <v>644.42</v>
+        <v>240.77</v>
       </c>
       <c r="K30" t="s">
         <v>15</v>
@@ -2009,10 +2072,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1">
-        <v>26758</v>
+        <v>68110</v>
       </c>
       <c r="B31" s="1">
-        <v>34105</v>
+        <v>33949</v>
       </c>
       <c r="C31" t="s">
         <v>77</v>
@@ -2027,16 +2090,16 @@
         <v>13</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H31" s="3">
-        <v>1812.75</v>
+        <v>680.25</v>
       </c>
       <c r="I31" s="3">
-        <v>124.2</v>
+        <v>35.83</v>
       </c>
       <c r="J31" s="3">
-        <v>1688.55</v>
+        <v>644.42</v>
       </c>
       <c r="K31" t="s">
         <v>15</v>
@@ -2044,10 +2107,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1">
-        <v>26814</v>
+        <v>68101</v>
       </c>
       <c r="B32" s="1">
-        <v>35957</v>
+        <v>34105</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
@@ -2062,16 +2125,16 @@
         <v>13</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H32" s="3">
-        <v>837.25</v>
+        <v>1812.75</v>
       </c>
       <c r="I32" s="3">
-        <v>45.88</v>
+        <v>124.2</v>
       </c>
       <c r="J32" s="3">
-        <v>791.37</v>
+        <v>1688.55</v>
       </c>
       <c r="K32" t="s">
         <v>15</v>
@@ -2079,10 +2142,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1">
-        <v>26800</v>
+        <v>68147</v>
       </c>
       <c r="B33" s="1">
-        <v>36658</v>
+        <v>35957</v>
       </c>
       <c r="C33" t="s">
         <v>81</v>
@@ -2097,16 +2160,16 @@
         <v>13</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="H33" s="3">
-        <v>28.0</v>
+        <v>483.25</v>
       </c>
       <c r="I33" s="3">
-        <v>0.54</v>
+        <v>23.22</v>
       </c>
       <c r="J33" s="3">
-        <v>27.46</v>
+        <v>460.03</v>
       </c>
       <c r="K33" t="s">
         <v>15</v>
@@ -2114,17 +2177,17 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1">
-        <v>26757</v>
+        <v>68100</v>
       </c>
       <c r="B34" s="1">
         <v>36819</v>
       </c>
       <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="E34" s="1">
         <v>30</v>
       </c>
@@ -2132,7 +2195,7 @@
         <v>13</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H34" s="3">
         <v>663.5</v>
@@ -2149,16 +2212,16 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1">
-        <v>26829</v>
+        <v>68160</v>
       </c>
       <c r="B35" s="1">
         <v>37206</v>
       </c>
       <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="E35" s="1">
         <v>30</v>
@@ -2184,16 +2247,16 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1">
-        <v>26828</v>
+        <v>68105</v>
       </c>
       <c r="B36" s="1">
-        <v>39687</v>
+        <v>41929</v>
       </c>
       <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="E36" s="1">
         <v>30</v>
@@ -2205,13 +2268,13 @@
         <v>14</v>
       </c>
       <c r="H36" s="3">
-        <v>75.0</v>
+        <v>2973.46</v>
       </c>
       <c r="I36" s="3">
-        <v>1.44</v>
+        <v>271.58</v>
       </c>
       <c r="J36" s="3">
-        <v>73.56</v>
+        <v>2701.88</v>
       </c>
       <c r="K36" t="s">
         <v>15</v>
@@ -2219,16 +2282,16 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1">
-        <v>26792</v>
+        <v>68120</v>
       </c>
       <c r="B37" s="1">
-        <v>41172</v>
+        <v>42170</v>
       </c>
       <c r="C37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="E37" s="1">
         <v>30</v>
@@ -2240,13 +2303,13 @@
         <v>14</v>
       </c>
       <c r="H37" s="3">
-        <v>78.25</v>
+        <v>130.35</v>
       </c>
       <c r="I37" s="3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J37" s="3">
-        <v>76.75</v>
+        <v>127.85</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
@@ -2254,17 +2317,17 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="1">
-        <v>26762</v>
+        <v>68168</v>
       </c>
       <c r="B38" s="1">
-        <v>41929</v>
+        <v>43241</v>
       </c>
       <c r="C38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="E38" s="1">
         <v>30</v>
       </c>
@@ -2272,16 +2335,16 @@
         <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H38" s="3">
-        <v>2973.46</v>
+        <v>117.75</v>
       </c>
       <c r="I38" s="3">
-        <v>271.58</v>
+        <v>2.26</v>
       </c>
       <c r="J38" s="3">
-        <v>2701.88</v>
+        <v>115.49</v>
       </c>
       <c r="K38" t="s">
         <v>15</v>
@@ -2289,17 +2352,17 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1">
-        <v>26810</v>
+        <v>68099</v>
       </c>
       <c r="B39" s="1">
-        <v>42170</v>
+        <v>43402</v>
       </c>
       <c r="C39" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="E39" s="1">
         <v>30</v>
       </c>
@@ -2307,16 +2370,16 @@
         <v>13</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H39" s="3">
-        <v>130.35</v>
+        <v>354.5</v>
       </c>
       <c r="I39" s="3">
-        <v>2.5</v>
+        <v>14.98</v>
       </c>
       <c r="J39" s="3">
-        <v>127.85</v>
+        <v>339.52</v>
       </c>
       <c r="K39" t="s">
         <v>15</v>
@@ -2324,17 +2387,17 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1">
-        <v>26839</v>
+        <v>68121</v>
       </c>
       <c r="B40" s="1">
-        <v>43241</v>
+        <v>45239</v>
       </c>
       <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="E40" s="1">
         <v>30</v>
       </c>
@@ -2342,16 +2405,16 @@
         <v>13</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H40" s="3">
-        <v>117.75</v>
+        <v>778.5</v>
       </c>
       <c r="I40" s="3">
-        <v>2.26</v>
+        <v>42.12</v>
       </c>
       <c r="J40" s="3">
-        <v>115.49</v>
+        <v>736.38</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
@@ -2359,17 +2422,17 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1">
-        <v>26756</v>
+        <v>68153</v>
       </c>
       <c r="B41" s="1">
-        <v>43402</v>
+        <v>45608</v>
       </c>
       <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="E41" s="1">
         <v>30</v>
       </c>
@@ -2377,16 +2440,16 @@
         <v>13</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H41" s="3">
-        <v>354.5</v>
+        <v>600.0</v>
       </c>
       <c r="I41" s="3">
-        <v>14.98</v>
+        <v>30.7</v>
       </c>
       <c r="J41" s="3">
-        <v>339.52</v>
+        <v>569.3</v>
       </c>
       <c r="K41" t="s">
         <v>15</v>
@@ -2394,17 +2457,17 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1">
-        <v>26859</v>
+        <v>68126</v>
       </c>
       <c r="B42" s="1">
-        <v>45608</v>
+        <v>45670</v>
       </c>
       <c r="C42" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="E42" s="1">
         <v>30</v>
       </c>
@@ -2412,16 +2475,16 @@
         <v>13</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H42" s="3">
-        <v>600.0</v>
+        <v>539.0</v>
       </c>
       <c r="I42" s="3">
-        <v>30.7</v>
+        <v>26.79</v>
       </c>
       <c r="J42" s="3">
-        <v>569.3</v>
+        <v>512.21</v>
       </c>
       <c r="K42" t="s">
         <v>15</v>
@@ -2429,17 +2492,17 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1">
-        <v>26788</v>
+        <v>68125</v>
       </c>
       <c r="B43" s="1">
-        <v>45670</v>
+        <v>45926</v>
       </c>
       <c r="C43" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="E43" s="1">
         <v>30</v>
       </c>
@@ -2447,16 +2510,16 @@
         <v>13</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H43" s="3">
-        <v>539.0</v>
+        <v>192.75</v>
       </c>
       <c r="I43" s="3">
-        <v>26.79</v>
+        <v>4.63</v>
       </c>
       <c r="J43" s="3">
-        <v>512.21</v>
+        <v>188.12</v>
       </c>
       <c r="K43" t="s">
         <v>15</v>
@@ -2464,17 +2527,17 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1">
-        <v>26864</v>
+        <v>68156</v>
       </c>
       <c r="B44" s="1">
         <v>46264</v>
       </c>
       <c r="C44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="E44" s="1">
         <v>30</v>
       </c>
@@ -2482,16 +2545,16 @@
         <v>13</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H44" s="3">
-        <v>400.0</v>
+        <v>275.0</v>
       </c>
       <c r="I44" s="3">
-        <v>17.9</v>
+        <v>9.9</v>
       </c>
       <c r="J44" s="3">
-        <v>382.1</v>
+        <v>265.1</v>
       </c>
       <c r="K44" t="s">
         <v>15</v>
@@ -2499,17 +2562,17 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1">
-        <v>26818</v>
+        <v>68141</v>
       </c>
       <c r="B45" s="1">
-        <v>48647</v>
+        <v>47455</v>
       </c>
       <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="E45" s="1">
         <v>30</v>
       </c>
@@ -2517,16 +2580,16 @@
         <v>13</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H45" s="3">
-        <v>234.75</v>
+        <v>651.2</v>
       </c>
       <c r="I45" s="3">
-        <v>7.32</v>
+        <v>33.97</v>
       </c>
       <c r="J45" s="3">
-        <v>227.43</v>
+        <v>617.23</v>
       </c>
       <c r="K45" t="s">
         <v>15</v>
@@ -2534,17 +2597,17 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1">
-        <v>26765</v>
+        <v>68149</v>
       </c>
       <c r="B46" s="1">
-        <v>50496</v>
+        <v>48647</v>
       </c>
       <c r="C46" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="E46" s="1">
         <v>30</v>
       </c>
@@ -2552,16 +2615,16 @@
         <v>13</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H46" s="3">
-        <v>105.5</v>
+        <v>234.75</v>
       </c>
       <c r="I46" s="3">
-        <v>2.03</v>
+        <v>7.32</v>
       </c>
       <c r="J46" s="3">
-        <v>103.47</v>
+        <v>227.43</v>
       </c>
       <c r="K46" t="s">
         <v>15</v>
@@ -2569,16 +2632,16 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1">
-        <v>26862</v>
+        <v>68108</v>
       </c>
       <c r="B47" s="1">
-        <v>52422</v>
+        <v>50496</v>
       </c>
       <c r="C47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="E47" s="1">
         <v>30</v>
@@ -2590,13 +2653,13 @@
         <v>26</v>
       </c>
       <c r="H47" s="3">
-        <v>79.5</v>
+        <v>105.5</v>
       </c>
       <c r="I47" s="3">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="J47" s="3">
-        <v>77.97</v>
+        <v>103.47</v>
       </c>
       <c r="K47" t="s">
         <v>15</v>
@@ -2604,17 +2667,17 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1">
-        <v>26866</v>
+        <v>68150</v>
       </c>
       <c r="B48" s="1">
-        <v>56381</v>
+        <v>52526</v>
       </c>
       <c r="C48" t="s">
+        <v>111</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="E48" s="1">
         <v>30</v>
       </c>
@@ -2622,16 +2685,16 @@
         <v>13</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H48" s="3">
-        <v>224.0</v>
+        <v>748.0</v>
       </c>
       <c r="I48" s="3">
-        <v>6.63</v>
+        <v>40.17</v>
       </c>
       <c r="J48" s="3">
-        <v>217.37</v>
+        <v>707.83</v>
       </c>
       <c r="K48" t="s">
         <v>15</v>
@@ -2639,17 +2702,17 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="1">
-        <v>26827</v>
+        <v>68130</v>
       </c>
       <c r="B49" s="1">
-        <v>57929</v>
+        <v>53933</v>
       </c>
       <c r="C49" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="E49" s="1">
         <v>30</v>
       </c>
@@ -2657,16 +2720,16 @@
         <v>13</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H49" s="3">
-        <v>25.0</v>
+        <v>651.2</v>
       </c>
       <c r="I49" s="3">
-        <v>0.48</v>
+        <v>33.97</v>
       </c>
       <c r="J49" s="3">
-        <v>24.52</v>
+        <v>617.23</v>
       </c>
       <c r="K49" t="s">
         <v>15</v>
@@ -2674,17 +2737,17 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="1">
-        <v>26817</v>
+        <v>68087</v>
       </c>
       <c r="B50" s="1">
-        <v>58283</v>
+        <v>55046</v>
       </c>
       <c r="C50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="E50" s="1">
         <v>30</v>
       </c>
@@ -2692,16 +2755,16 @@
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H50" s="3">
-        <v>39.25</v>
+        <v>117.45</v>
       </c>
       <c r="I50" s="3">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="J50" s="3">
-        <v>38.5</v>
+        <v>115.2</v>
       </c>
       <c r="K50" t="s">
         <v>15</v>
@@ -2709,16 +2772,16 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="1">
-        <v>26764</v>
+        <v>68157</v>
       </c>
       <c r="B51" s="1">
-        <v>58634</v>
+        <v>56381</v>
       </c>
       <c r="C51" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="E51" s="1">
         <v>30</v>
@@ -2730,13 +2793,13 @@
         <v>26</v>
       </c>
       <c r="H51" s="3">
-        <v>1475.25</v>
+        <v>224.0</v>
       </c>
       <c r="I51" s="3">
-        <v>87.48</v>
+        <v>6.63</v>
       </c>
       <c r="J51" s="3">
-        <v>1387.77</v>
+        <v>217.37</v>
       </c>
       <c r="K51" t="s">
         <v>15</v>
@@ -2744,17 +2807,17 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="1">
-        <v>26780</v>
+        <v>68107</v>
       </c>
       <c r="B52" s="1">
-        <v>60658</v>
+        <v>58634</v>
       </c>
       <c r="C52" t="s">
+        <v>119</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="E52" s="1">
         <v>30</v>
       </c>
@@ -2762,16 +2825,16 @@
         <v>13</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H52" s="3">
-        <v>168.25</v>
+        <v>1475.25</v>
       </c>
       <c r="I52" s="3">
-        <v>3.23</v>
+        <v>87.48</v>
       </c>
       <c r="J52" s="3">
-        <v>165.02</v>
+        <v>1387.77</v>
       </c>
       <c r="K52" t="s">
         <v>15</v>
@@ -2779,16 +2842,16 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="1">
-        <v>26834</v>
+        <v>68080</v>
       </c>
       <c r="B53" s="1">
-        <v>62143</v>
+        <v>59449</v>
       </c>
       <c r="C53" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="E53" s="1">
         <v>30</v>
@@ -2800,13 +2863,13 @@
         <v>26</v>
       </c>
       <c r="H53" s="3">
-        <v>638.55</v>
+        <v>126.75</v>
       </c>
       <c r="I53" s="3">
-        <v>33.16</v>
+        <v>2.43</v>
       </c>
       <c r="J53" s="3">
-        <v>605.39</v>
+        <v>124.32</v>
       </c>
       <c r="K53" t="s">
         <v>15</v>
@@ -2814,17 +2877,17 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="1">
-        <v>26804</v>
+        <v>68117</v>
       </c>
       <c r="B54" s="1">
-        <v>62272</v>
+        <v>60658</v>
       </c>
       <c r="C54" t="s">
+        <v>123</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="E54" s="1">
         <v>30</v>
       </c>
@@ -2832,16 +2895,16 @@
         <v>13</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H54" s="3">
-        <v>25.0</v>
+        <v>168.25</v>
       </c>
       <c r="I54" s="3">
-        <v>0.48</v>
+        <v>3.23</v>
       </c>
       <c r="J54" s="3">
-        <v>24.52</v>
+        <v>165.02</v>
       </c>
       <c r="K54" t="s">
         <v>15</v>
@@ -2849,17 +2912,17 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1">
-        <v>26833</v>
+        <v>68086</v>
       </c>
       <c r="B55" s="1">
-        <v>62411</v>
+        <v>61998</v>
       </c>
       <c r="C55" t="s">
+        <v>125</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="E55" s="1">
         <v>30</v>
       </c>
@@ -2867,16 +2930,16 @@
         <v>13</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H55" s="3">
-        <v>229.05</v>
+        <v>160.75</v>
       </c>
       <c r="I55" s="3">
-        <v>6.95</v>
+        <v>3.09</v>
       </c>
       <c r="J55" s="3">
-        <v>222.1</v>
+        <v>157.66</v>
       </c>
       <c r="K55" t="s">
         <v>15</v>
@@ -2884,17 +2947,17 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="1">
-        <v>26813</v>
+        <v>68164</v>
       </c>
       <c r="B56" s="1">
-        <v>64846</v>
+        <v>62143</v>
       </c>
       <c r="C56" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="E56" s="1">
         <v>30</v>
       </c>
@@ -2902,16 +2965,16 @@
         <v>13</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H56" s="3">
-        <v>1589.15</v>
+        <v>638.55</v>
       </c>
       <c r="I56" s="3">
-        <v>99.87</v>
+        <v>33.16</v>
       </c>
       <c r="J56" s="3">
-        <v>1489.28</v>
+        <v>605.39</v>
       </c>
       <c r="K56" t="s">
         <v>15</v>
@@ -2919,17 +2982,17 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1">
-        <v>26786</v>
+        <v>68163</v>
       </c>
       <c r="B57" s="1">
-        <v>86298</v>
+        <v>62411</v>
       </c>
       <c r="C57" t="s">
+        <v>129</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="E57" s="1">
         <v>30</v>
       </c>
@@ -2937,16 +3000,16 @@
         <v>13</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H57" s="3">
-        <v>1207.2</v>
+        <v>229.05</v>
       </c>
       <c r="I57" s="3">
-        <v>69.56</v>
+        <v>6.95</v>
       </c>
       <c r="J57" s="3">
-        <v>1137.64</v>
+        <v>222.1</v>
       </c>
       <c r="K57" t="s">
         <v>15</v>
@@ -2954,17 +3017,17 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1">
-        <v>26785</v>
+        <v>68146</v>
       </c>
       <c r="B58" s="1">
-        <v>93767</v>
+        <v>64846</v>
       </c>
       <c r="C58" t="s">
+        <v>131</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E58" s="1">
         <v>30</v>
       </c>
@@ -2972,16 +3035,16 @@
         <v>13</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H58" s="3">
-        <v>452.7</v>
+        <v>704.15</v>
       </c>
       <c r="I58" s="3">
-        <v>21.27</v>
+        <v>37.36</v>
       </c>
       <c r="J58" s="3">
-        <v>431.43</v>
+        <v>666.79</v>
       </c>
       <c r="K58" t="s">
         <v>15</v>
@@ -2989,16 +3052,16 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="1">
-        <v>26784</v>
+        <v>68165</v>
       </c>
       <c r="B59" s="1">
-        <v>96935</v>
+        <v>70508</v>
       </c>
       <c r="C59" t="s">
+        <v>133</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="E59" s="1">
         <v>30</v>
@@ -3010,13 +3073,13 @@
         <v>26</v>
       </c>
       <c r="H59" s="3">
-        <v>65.95</v>
+        <v>200.0</v>
       </c>
       <c r="I59" s="3">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="J59" s="3">
-        <v>64.68</v>
+        <v>194.9</v>
       </c>
       <c r="K59" t="s">
         <v>15</v>
@@ -3024,17 +3087,17 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1">
-        <v>26869</v>
+        <v>68159</v>
       </c>
       <c r="B60" s="1">
-        <v>116517</v>
+        <v>79568</v>
       </c>
       <c r="C60" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="E60" s="1">
         <v>30</v>
       </c>
@@ -3042,16 +3105,16 @@
         <v>13</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H60" s="3">
-        <v>614.0</v>
+        <v>674.0</v>
       </c>
       <c r="I60" s="3">
-        <v>31.59</v>
+        <v>35.43</v>
       </c>
       <c r="J60" s="3">
-        <v>582.41</v>
+        <v>638.57</v>
       </c>
       <c r="K60" t="s">
         <v>15</v>
@@ -3059,17 +3122,17 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1">
-        <v>26832</v>
+        <v>68119</v>
       </c>
       <c r="B61" s="1">
-        <v>149615</v>
+        <v>82368</v>
       </c>
       <c r="C61" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="E61" s="1">
         <v>30</v>
       </c>
@@ -3077,16 +3140,16 @@
         <v>13</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H61" s="3">
-        <v>48.6</v>
+        <v>200.0</v>
       </c>
       <c r="I61" s="3">
-        <v>0.93</v>
+        <v>5.1</v>
       </c>
       <c r="J61" s="3">
-        <v>47.67</v>
+        <v>194.9</v>
       </c>
       <c r="K61" t="s">
         <v>15</v>
@@ -3094,36 +3157,421 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="1">
-        <v>26852</v>
+        <v>68124</v>
       </c>
       <c r="B62" s="1">
+        <v>86298</v>
+      </c>
+      <c r="C62" t="s">
+        <v>139</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" s="1">
+        <v>30</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1207.2</v>
+      </c>
+      <c r="I62" s="3">
+        <v>69.56</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1137.64</v>
+      </c>
+      <c r="K62" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="1">
+        <v>68138</v>
+      </c>
+      <c r="B63" s="1">
+        <v>86784</v>
+      </c>
+      <c r="C63" t="s">
+        <v>141</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="1">
+        <v>30</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="3">
+        <v>356.25</v>
+      </c>
+      <c r="I63" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="J63" s="3">
+        <v>341.15</v>
+      </c>
+      <c r="K63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="1">
+        <v>68123</v>
+      </c>
+      <c r="B64" s="1">
+        <v>93767</v>
+      </c>
+      <c r="C64" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E64" s="1">
+        <v>30</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H64" s="3">
+        <v>452.7</v>
+      </c>
+      <c r="I64" s="3">
+        <v>21.27</v>
+      </c>
+      <c r="J64" s="3">
+        <v>431.43</v>
+      </c>
+      <c r="K64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="1">
+        <v>68082</v>
+      </c>
+      <c r="B65" s="1">
+        <v>95750</v>
+      </c>
+      <c r="C65" t="s">
+        <v>145</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" s="1">
+        <v>30</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H65" s="3">
+        <v>309.75</v>
+      </c>
+      <c r="I65" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="J65" s="3">
+        <v>297.63</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="1">
+        <v>68167</v>
+      </c>
+      <c r="B66" s="1">
+        <v>116517</v>
+      </c>
+      <c r="C66" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E66" s="1">
+        <v>30</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H66" s="3">
+        <v>614.0</v>
+      </c>
+      <c r="I66" s="3">
+        <v>31.59</v>
+      </c>
+      <c r="J66" s="3">
+        <v>582.41</v>
+      </c>
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="1">
+        <v>68155</v>
+      </c>
+      <c r="B67" s="1">
+        <v>138228</v>
+      </c>
+      <c r="C67" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E67" s="1">
+        <v>30</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67" s="3">
+        <v>212.0</v>
+      </c>
+      <c r="I67" s="3">
+        <v>5.86</v>
+      </c>
+      <c r="J67" s="3">
+        <v>206.14</v>
+      </c>
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="1">
+        <v>68133</v>
+      </c>
+      <c r="B68" s="1">
+        <v>149718</v>
+      </c>
+      <c r="C68" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" s="1">
+        <v>30</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68" s="3">
+        <v>284.0</v>
+      </c>
+      <c r="I68" s="3">
+        <v>10.47</v>
+      </c>
+      <c r="J68" s="3">
+        <v>273.53</v>
+      </c>
+      <c r="K68" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="1">
+        <v>68081</v>
+      </c>
+      <c r="B69" s="1">
+        <v>151151</v>
+      </c>
+      <c r="C69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69" s="1">
+        <v>30</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="3">
+        <v>1031.0</v>
+      </c>
+      <c r="I69" s="3">
+        <v>58.28</v>
+      </c>
+      <c r="J69" s="3">
+        <v>972.72</v>
+      </c>
+      <c r="K69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="1">
+        <v>68145</v>
+      </c>
+      <c r="B70" s="1">
+        <v>156136</v>
+      </c>
+      <c r="C70" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70" s="1">
+        <v>30</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H70" s="3">
+        <v>1416.0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>82.92</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1333.08</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="1">
+        <v>68161</v>
+      </c>
+      <c r="B71" s="1">
+        <v>156814</v>
+      </c>
+      <c r="C71" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" s="1">
+        <v>30</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" s="3">
+        <v>213.2</v>
+      </c>
+      <c r="I71" s="3">
+        <v>5.94</v>
+      </c>
+      <c r="J71" s="3">
+        <v>207.26</v>
+      </c>
+      <c r="K71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="1">
+        <v>68078</v>
+      </c>
+      <c r="B72" s="1">
+        <v>156888</v>
+      </c>
+      <c r="C72" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E72" s="1">
+        <v>30</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="3">
+        <v>142.0</v>
+      </c>
+      <c r="I72" s="3">
+        <v>2.73</v>
+      </c>
+      <c r="J72" s="3">
+        <v>139.27</v>
+      </c>
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="1">
+        <v>68140</v>
+      </c>
+      <c r="B73" s="1">
         <v>157530</v>
       </c>
-      <c r="C62" t="s">
-        <v>140</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E62" s="1">
-        <v>30</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="C73" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E73" s="1">
+        <v>30</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H73" s="3">
         <v>200.0</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I73" s="3">
         <v>5.1</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J73" s="3">
         <v>194.9</v>
       </c>
-      <c r="K62" t="s">
+      <c r="K73" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3165,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -3180,13 +3628,13 @@
         <v>7</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>9</v>
@@ -3195,21 +3643,21 @@
         <v>10</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1">
-        <v>26781</v>
+        <v>68118</v>
       </c>
       <c r="B2" s="1">
         <v>15862</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -3236,21 +3684,21 @@
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1">
-        <v>26783</v>
+        <v>68122</v>
       </c>
       <c r="B3" s="1">
         <v>28826</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -3277,21 +3725,21 @@
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>26763</v>
+        <v>68106</v>
       </c>
       <c r="B4" s="1">
         <v>28842</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E4" s="1">
         <v>30</v>
@@ -3318,21 +3766,21 @@
         <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <v>26761</v>
+        <v>68104</v>
       </c>
       <c r="B5" s="1">
         <v>32605</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="E5" s="1">
         <v>30</v>
@@ -3359,21 +3807,21 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1">
-        <v>26812</v>
+        <v>68148</v>
       </c>
       <c r="B6" s="1">
         <v>32614</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E6" s="1">
         <v>30</v>
@@ -3400,7 +3848,7 @@
         <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3441,13 +3889,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -3462,22 +3910,22 @@
         <v>5</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>9</v>
@@ -3488,22 +3936,22 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1">
-        <v>26760</v>
+        <v>68092</v>
       </c>
       <c r="B2" s="1">
         <v>80161701</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D2" s="1">
         <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="G2" s="1">
         <v>30</v>
@@ -3512,25 +3960,25 @@
         <v>13</v>
       </c>
       <c r="I2" s="3">
-        <v>535.33275862069</v>
+        <v>535.83620689655</v>
       </c>
       <c r="J2" s="3">
-        <v>6209.86</v>
+        <v>6215.7</v>
       </c>
       <c r="K2" s="3">
-        <v>5353.3275862069</v>
+        <v>5358.3620689655</v>
       </c>
       <c r="L2" s="3">
-        <v>4817.9948275862</v>
+        <v>4822.525862069</v>
       </c>
       <c r="M2" s="3">
-        <v>770.87917241379</v>
+        <v>771.60413793103</v>
       </c>
       <c r="N2" s="3">
-        <v>60.224935344828</v>
+        <v>60.281573275862</v>
       </c>
       <c r="O2" s="3">
-        <v>6385.1814784483</v>
+        <v>6391.1863577586</v>
       </c>
       <c r="P2" t="s">
         <v>15</v>
@@ -3538,22 +3986,22 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1">
-        <v>26796</v>
+        <v>68096</v>
       </c>
       <c r="B3" s="1">
         <v>80161701</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1">
         <v>10859</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="G3" s="1">
         <v>30</v>
@@ -3588,22 +4036,22 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1">
-        <v>26775</v>
+        <v>68091</v>
       </c>
       <c r="B4" s="1">
         <v>80161701</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D4" s="1">
         <v>17507</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G4" s="1">
         <v>30</v>
@@ -3612,25 +4060,25 @@
         <v>13</v>
       </c>
       <c r="I4" s="3">
-        <v>214.35948275862</v>
+        <v>218.17586206897</v>
       </c>
       <c r="J4" s="3">
-        <v>2486.57</v>
+        <v>2530.84</v>
       </c>
       <c r="K4" s="3">
-        <v>2143.5948275862</v>
+        <v>2181.7586206897</v>
       </c>
       <c r="L4" s="3">
-        <v>1929.2353448276</v>
+        <v>1963.5827586207</v>
       </c>
       <c r="M4" s="3">
-        <v>308.67765517241</v>
+        <v>314.17324137931</v>
       </c>
       <c r="N4" s="3">
-        <v>24.115441810345</v>
+        <v>24.544784482759</v>
       </c>
       <c r="O4" s="3">
-        <v>2556.7727306034</v>
+        <v>2602.2925948276</v>
       </c>
       <c r="P4" t="s">
         <v>15</v>
@@ -3638,22 +4086,22 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
-        <v>26779</v>
+        <v>68090</v>
       </c>
       <c r="B5" s="1">
         <v>80161701</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D5" s="1">
         <v>25918</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="G5" s="1">
         <v>30</v>
@@ -3662,25 +4110,25 @@
         <v>13</v>
       </c>
       <c r="I5" s="3">
-        <v>451.79568965517</v>
+        <v>456.55344827586</v>
       </c>
       <c r="J5" s="3">
-        <v>5240.83</v>
+        <v>5296.02</v>
       </c>
       <c r="K5" s="3">
-        <v>4517.9568965517</v>
+        <v>4565.5344827586</v>
       </c>
       <c r="L5" s="3">
-        <v>4066.1612068966</v>
+        <v>4108.9810344828</v>
       </c>
       <c r="M5" s="3">
-        <v>650.58579310345</v>
+        <v>657.43696551724</v>
       </c>
       <c r="N5" s="3">
-        <v>50.827015086207</v>
+        <v>51.362262931034</v>
       </c>
       <c r="O5" s="3">
-        <v>5388.7930883621</v>
+        <v>5445.5412543103</v>
       </c>
       <c r="P5" t="s">
         <v>15</v>
@@ -3688,22 +4136,22 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
-        <v>26774</v>
+        <v>68102</v>
       </c>
       <c r="B6" s="1">
         <v>80161701</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D6" s="1">
         <v>31622</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="G6" s="1">
         <v>30</v>
@@ -3738,22 +4186,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
-        <v>26766</v>
+        <v>68109</v>
       </c>
       <c r="B7" s="1">
         <v>80161701</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D7" s="1">
         <v>31624</v>
       </c>
       <c r="E7" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="G7" s="1">
         <v>30</v>
@@ -3762,25 +4210,25 @@
         <v>13</v>
       </c>
       <c r="I7" s="3">
-        <v>125.63362068966</v>
+        <v>111.59913793103</v>
       </c>
       <c r="J7" s="3">
-        <v>1457.35</v>
+        <v>1294.55</v>
       </c>
       <c r="K7" s="3">
-        <v>1256.3362068966</v>
+        <v>1115.9913793103</v>
       </c>
       <c r="L7" s="3">
-        <v>1130.7025862069</v>
+        <v>1004.3922413793</v>
       </c>
       <c r="M7" s="3">
-        <v>180.9124137931</v>
+        <v>160.70275862069</v>
       </c>
       <c r="N7" s="3">
-        <v>14.133782327586</v>
+        <v>12.554903017241</v>
       </c>
       <c r="O7" s="3">
-        <v>1498.4950107759</v>
+        <v>1331.0987176724</v>
       </c>
       <c r="P7" t="s">
         <v>15</v>
@@ -3788,22 +4236,22 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
-        <v>26771</v>
+        <v>68112</v>
       </c>
       <c r="B8" s="1">
         <v>80161701</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D8" s="1">
         <v>31711</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="G8" s="1">
         <v>30</v>
